--- a/examples/data/basis.xlsx
+++ b/examples/data/basis.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,26 +519,6 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>alpha_pct</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>alpha_flat</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>beta_pct</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>gamma_flat</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
           <t>surrender_value_table</t>
         </is>
       </c>
@@ -611,7 +591,7 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>SURRENDER_STD</t>
         </is>
@@ -633,9 +613,6 @@
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>80000</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -653,9 +630,6 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>150000</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -673,9 +647,6 @@
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>100000</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -693,9 +664,6 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>180000</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -713,9 +681,6 @@
           <t>LAPSE_GA</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>40000</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -733,9 +698,6 @@
           <t>LAPSE_FC</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>200000</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -752,9 +714,6 @@
         <is>
           <t>LAPSE_GA</t>
         </is>
-      </c>
-      <c r="T9" t="n">
-        <v>350000</v>
       </c>
     </row>
   </sheetData>

--- a/examples/data/basis.xlsx
+++ b/examples/data/basis.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,11 @@
           <t>surrender_value_table</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>state_model</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,6 +599,11 @@
       <c r="S2" t="inlineStr">
         <is>
           <t>SURRENDER_STD</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>WAIVER</t>
         </is>
       </c>
     </row>
